--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d158aa81f07d6af9/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{DA15A839-AA70-4E44-AB2C-F2FB308315F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BD05F59-A927-4C1B-9452-294284BF0E2A}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{DA15A839-AA70-4E44-AB2C-F2FB308315F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F23610-820C-442A-9890-43E4E80819E3}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" xr2:uid="{28DF0FFF-81C1-462E-A008-789CA0B71480}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{28DF0FFF-81C1-462E-A008-789CA0B71480}"/>
   </bookViews>
   <sheets>
     <sheet name="Book1" sheetId="1" r:id="rId1"/>
@@ -2409,6 +2409,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2729,6 +2733,7 @@
   <dimension ref="A1:M268"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2900,6 +2905,9 @@
       <c r="L5" t="s">
         <v>16</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danna\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37730C6D-809D-492D-9A37-A55EA938EEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99118129-2381-488D-AF51-22DD33ACBB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{28DF0FFF-81C1-462E-A008-789CA0B71480}"/>
   </bookViews>
@@ -2918,9 +2918,6 @@
       <c r="L5" t="s">
         <v>614</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
